--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/TENNESSEE_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/TENNESSEE_2011.xlsx
@@ -409,7 +409,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="4">
@@ -661,7 +661,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="18">
@@ -1795,7 +1795,7 @@
         <v>7</v>
       </c>
       <c r="D80">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="81">
@@ -1831,7 +1831,7 @@
         <v>7</v>
       </c>
       <c r="D82">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="83">
@@ -1957,7 +1957,7 @@
         <v>7</v>
       </c>
       <c r="D89">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="90">
@@ -2767,7 +2767,7 @@
         <v>7</v>
       </c>
       <c r="D134">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="135">
@@ -2785,7 +2785,7 @@
         <v>7</v>
       </c>
       <c r="D135">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="136">
@@ -2929,7 +2929,7 @@
         <v>7</v>
       </c>
       <c r="D143">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="144">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C156">
@@ -3361,7 +3361,7 @@
         <v>7</v>
       </c>
       <c r="D167">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="168">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C172">
@@ -3595,7 +3595,7 @@
         <v>71</v>
       </c>
       <c r="D180">
-        <v>0.009906515976001</v>
+        <v>0.009906515976001002</v>
       </c>
     </row>
     <row r="181">
@@ -3991,7 +3991,7 @@
         <v>7</v>
       </c>
       <c r="D202">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="203">
@@ -4855,7 +4855,7 @@
         <v>7</v>
       </c>
       <c r="D250">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="251">
@@ -4927,7 +4927,7 @@
         <v>7</v>
       </c>
       <c r="D254">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="255">
@@ -4981,7 +4981,7 @@
         <v>7</v>
       </c>
       <c r="D257">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="258">
@@ -6889,7 +6889,7 @@
         <v>7</v>
       </c>
       <c r="D363">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="364">
@@ -6943,7 +6943,7 @@
         <v>7</v>
       </c>
       <c r="D366">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="367">
@@ -7123,7 +7123,7 @@
         <v>7</v>
       </c>
       <c r="D376">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="377">
@@ -7483,7 +7483,7 @@
         <v>7</v>
       </c>
       <c r="D396">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="397">
@@ -7699,7 +7699,7 @@
         <v>7</v>
       </c>
       <c r="D408">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="409">
@@ -7933,7 +7933,7 @@
         <v>7</v>
       </c>
       <c r="D421">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="422">
@@ -8401,7 +8401,7 @@
         <v>7</v>
       </c>
       <c r="D447">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="448">
@@ -8869,7 +8869,7 @@
         <v>71</v>
       </c>
       <c r="D473">
-        <v>0.009906515976001</v>
+        <v>0.009906515976001002</v>
       </c>
     </row>
     <row r="474">
@@ -9085,7 +9085,7 @@
         <v>7</v>
       </c>
       <c r="D485">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="486">
@@ -9391,7 +9391,7 @@
         <v>7</v>
       </c>
       <c r="D502">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="503">
@@ -9427,7 +9427,7 @@
         <v>7</v>
       </c>
       <c r="D504">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="505">
@@ -9913,7 +9913,7 @@
         <v>7</v>
       </c>
       <c r="D531">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="532">
@@ -10363,7 +10363,7 @@
         <v>7</v>
       </c>
       <c r="D556">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="557">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C564">
@@ -10543,7 +10543,7 @@
         <v>7</v>
       </c>
       <c r="D566">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="567">
@@ -10777,7 +10777,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="580">
@@ -11569,7 +11569,7 @@
         <v>7</v>
       </c>
       <c r="D623">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="624">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C628">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C647">
@@ -12199,7 +12199,7 @@
         <v>7</v>
       </c>
       <c r="D658">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="659">
@@ -14035,7 +14035,7 @@
         <v>7</v>
       </c>
       <c r="D760">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="761">
@@ -14233,7 +14233,7 @@
         <v>7</v>
       </c>
       <c r="D771">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="772">
@@ -15583,7 +15583,7 @@
         <v>7</v>
       </c>
       <c r="D846">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="847">
@@ -16159,7 +16159,7 @@
         <v>7</v>
       </c>
       <c r="D878">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="879">
@@ -16483,7 +16483,7 @@
         <v>7</v>
       </c>
       <c r="D896">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="897">
@@ -17329,7 +17329,7 @@
         <v>7</v>
       </c>
       <c r="D943">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="944">
@@ -17581,7 +17581,7 @@
         <v>7</v>
       </c>
       <c r="D957">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="958">
@@ -18175,7 +18175,7 @@
         <v>7</v>
       </c>
       <c r="D990">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="991">
@@ -18301,7 +18301,7 @@
         <v>7</v>
       </c>
       <c r="D997">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="998">
@@ -18337,7 +18337,7 @@
         <v>7</v>
       </c>
       <c r="D999">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="1000">
@@ -18589,7 +18589,7 @@
         <v>7</v>
       </c>
       <c r="D1013">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="1014">
@@ -18733,7 +18733,7 @@
         <v>7</v>
       </c>
       <c r="D1021">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="1022">
@@ -19399,7 +19399,7 @@
         <v>7</v>
       </c>
       <c r="D1058">
-        <v>0.000976698758197</v>
+        <v>0.0009766987581970002</v>
       </c>
     </row>
     <row r="1059">
